--- a/src/test.dataExchange/resources/testData/dataExchangeDemoData.xlsx
+++ b/src/test.dataExchange/resources/testData/dataExchangeDemoData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rachowdhury\Documents\Software\mtf-dm-automation-test-api\src\test.dataExchange\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mthomas\Documents\mtf-dm-automation-test-api\src\test.dataExchange\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF9F20E-BEAB-426A-B2F6-245331CA78F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E537E3F-A822-4752-B4C1-5B4C95009D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28930" yWindow="910" windowWidth="22360" windowHeight="9640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MFP" sheetId="1" r:id="rId1"/>
@@ -25,22 +25,22 @@
     <t>test_case_id</t>
   </si>
   <si>
-    <t xml:space="preserve"> sql_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> sql_query</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> expected_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> select ndc_eleven, effective_date from mfp;</t>
-  </si>
-  <si>
     <t>Test NDC-11 and Effective Date Dynamicly No Function needed</t>
   </si>
   <si>
-    <t xml:space="preserve"> NDC-11, MFP Effective Date</t>
+    <t>MFP Effective Date, Single MFP per 30 DES, Type of Update</t>
+  </si>
+  <si>
+    <t>sql_description</t>
+  </si>
+  <si>
+    <t>sql_query</t>
+  </si>
+  <si>
+    <t>expected_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SELECT mfp_eff_dt, mfp_per_30, update_type FROM price_eff_dt</t>
   </si>
 </sst>
 </file>
@@ -886,7 +886,7 @@
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.21875" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
@@ -896,13 +896,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/src/test.dataExchange/resources/testData/dataExchangeDemoData.xlsx
+++ b/src/test.dataExchange/resources/testData/dataExchangeDemoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mthomas\Documents\mtf-dm-automation-test-api\src\test.dataExchange\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E537E3F-A822-4752-B4C1-5B4C95009D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BBCFC8-1413-4354-8772-E0A56EAD0EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28930" yWindow="910" windowWidth="22360" windowHeight="9640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20030" yWindow="3840" windowWidth="21730" windowHeight="11570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MFP" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
     <t>Test NDC-11 and Effective Date Dynamicly No Function needed</t>
   </si>
   <si>
-    <t>MFP Effective Date, Single MFP per 30 DES, Type of Update</t>
-  </si>
-  <si>
     <t>sql_description</t>
   </si>
   <si>
@@ -40,7 +37,10 @@
     <t>expected_value</t>
   </si>
   <si>
-    <t xml:space="preserve"> SELECT mfp_eff_dt, mfp_per_30, update_type FROM price_eff_dt</t>
+    <t>SELECT mfp_per_30, mfp_per_unit, mfp_per_package FROM price_eff_dt</t>
+  </si>
+  <si>
+    <t>Single MFP per 30 DES, NDC-9 MFP per Unit Price, NDC-11 MFP per Package Price</t>
   </si>
 </sst>
 </file>
@@ -896,13 +896,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -913,10 +913,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
